--- a/samples/ss_byoli_ingest.xlsx
+++ b/samples/ss_byoli_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,65 +536,70 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bus 150 kV</t>
+          <t>Bus HV</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Bus LV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Jumlah Trafo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Kapasitor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Catatan Simbol</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit Bay</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Wilayah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
@@ -633,24 +638,25 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -686,41 +692,46 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>BYOLI7</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>BYOLI</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>2 IBT x 500 MVA (unit 1,2)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -753,30 +764,31 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>4 seksi bus (A/B/C/D) + Kopel A, Kopel B; 60 MVA</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -809,30 +821,31 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -865,30 +878,31 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>3x60 MVA + 50 MVAR</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -921,34 +935,35 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -981,34 +996,35 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1041,34 +1057,35 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>3x60 MVA; batas ke Subsistem Pedan 1,2</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>SOURCE_BOUNDARY</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1101,34 +1118,35 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_byoli_ingest.xlsx
+++ b/samples/ss_byoli_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,6 +1147,169 @@
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jelok</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>JELOK</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PLTA Jelok</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>KIT_JELOK</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Pembangkit</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PLTA Timo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>KIT_TIMO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Pembangkit</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1159,7 +1322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1673,6 +1836,187 @@
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SUTT Boyolali - Jelok</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BYOLI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>JELOK</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sangat Rawan</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Outlet PLTA Jelok</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>KIT_JELOK</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>JELOK</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Outlet PLTA Timo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>KIT_TIMO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>JELOK</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_byoli_ingest.xlsx
+++ b/samples/ss_byoli_ingest.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/samples/ss_byoli_ingest.xlsx
+++ b/samples/ss_byoli_ingest.xlsx
@@ -2029,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2055,25 +2055,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Tegangan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
@@ -2085,7 +2090,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UNGA7</t>
+          <t>UNGRN7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2100,23 +2105,28 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>500 kV</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2124,7 +2134,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PDAN7</t>
+          <t>PEDAN7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2139,23 +2149,28 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="inlineStr">
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>500 kV</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_byoli_ingest.xlsx
+++ b/samples/ss_byoli_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,7 +664,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 1,2 Boyolali 500/150 kV</t>
+          <t>IBT 1 Boyolali 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -701,14 +701,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT x 500 MVA (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -739,37 +735,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Boyolali (bus 150 kV)</t>
+          <t>IBT 2 Boyolali 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>IBT 2 BYOLI7</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>BYOLI7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>BYOLI</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>4 seksi bus (A/B/C/D) + Kopel A, Kopel B; 60 MVA</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -779,10 +785,14 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -796,12 +806,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Boyolali Ring / Banaran</t>
+          <t>Boyolali (bus 150 kV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BRNGI</t>
+          <t>BYOLI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -810,7 +820,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -824,7 +834,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2x60 MVA</t>
+          <t>4 seksi bus (A/B/C/D) + Kopel A, Kopel B; 60 MVA</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -853,12 +863,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bendono</t>
+          <t>Boyolali Ring / Banaran</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BDONO</t>
+          <t>BRNGI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -881,7 +891,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3x60 MVA + 50 MVAR</t>
+          <t>2x60 MVA</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -910,12 +920,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mojosongo</t>
+          <t>Bendono</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MJNGO</t>
+          <t>BDONO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -938,7 +948,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2x60 MVA</t>
+          <t>3x60 MVA + 50 MVAR</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -950,14 +960,10 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -971,12 +977,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mangkunegaran</t>
+          <t>Mojosongo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MKRAN</t>
+          <t>MJNGO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -985,7 +991,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1032,12 +1038,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jajar</t>
+          <t>Mangkunegaran</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JAJAR</t>
+          <t>MKRAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1060,7 +1066,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3x60 MVA; batas ke Subsistem Pedan 1,2</t>
+          <t>2x60 MVA</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1069,17 +1075,17 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1093,12 +1099,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gondangrejo</t>
+          <t>Jajar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GDRJO</t>
+          <t>JAJAR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1121,7 +1127,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2x60 MVA</t>
+          <t>3x60 MVA; batas ke Subsistem Pedan 1,2</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1130,17 +1136,17 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1154,12 +1160,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jelok</t>
+          <t>Gondangrejo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JELOK</t>
+          <t>GDRJO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1168,7 +1174,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1180,7 +1186,11 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2x60 MVA</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
@@ -1195,7 +1205,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1211,17 +1221,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PLTA Jelok</t>
+          <t>Jelok</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KIT_JELOK</t>
+          <t>JELOK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1247,10 +1257,14 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1264,12 +1278,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PLTA Timo</t>
+          <t>PLTA Jelok</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KIT_TIMO</t>
+          <t>KIT_JELOK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1310,6 +1324,59 @@
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PLTA Timo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>KIT_TIMO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Pembangkit</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
